--- a/artfynd/A 59971-2025 artfynd.xlsx
+++ b/artfynd/A 59971-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59971-2025 artfynd.xlsx
+++ b/artfynd/A 59971-2025 artfynd.xlsx
@@ -973,7 +973,7 @@
         <v>128710147</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
